--- a/output/pdf_financials_xlsx/LPK.xlsx
+++ b/output/pdf_financials_xlsx/LPK.xlsx
@@ -1219,25 +1219,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.901382</v>
+        <v>-1.901382</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5.534782</v>
+        <v>-5.534782</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>9.596</v>
+        <v>-9.596</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9.782</v>
+        <v>-9.782</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>4.609</v>
+        <v>-4.609</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.8</v>
+        <v>-3.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.221</v>
+        <v>-2.221</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-14.883</v>
@@ -1503,25 +1503,25 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.901382</v>
+        <v>-1.901382</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.534782</v>
+        <v>-5.534782</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>9.596</v>
+        <v>-9.596</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9.782</v>
+        <v>-9.782</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4.609</v>
+        <v>-4.609</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.8</v>
+        <v>-3.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.221</v>
+        <v>-2.221</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-14.883</v>
@@ -1668,25 +1668,25 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.901382</v>
+        <v>-1.901382</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5.534782</v>
+        <v>-5.534782</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>9.596</v>
+        <v>-9.596</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>9.782</v>
+        <v>-9.782</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.609</v>
+        <v>-4.609</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.8</v>
+        <v>-3.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.221</v>
+        <v>-2.221</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-14.883</v>
@@ -1833,25 +1833,25 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>14.626015</v>
+        <v>-14.626015</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>39.534157</v>
+        <v>-39.534157</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>53.311111</v>
+        <v>-53.311111</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>81.516667</v>
+        <v>-81.516667</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>92.18000000000001</v>
+        <v>-92.18000000000001</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>95</v>
+        <v>-95</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>111.05</v>
+        <v>-111.05</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>-114.484615</v>
@@ -1896,25 +1896,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.901382</v>
+        <v>-1.901382</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.617777</v>
+        <v>-5.451787</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9.654</v>
+        <v>-9.538</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>9.842000000000001</v>
+        <v>-9.722</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.637</v>
+        <v>-4.581</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.805</v>
+        <v>-3.795</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.221</v>
+        <v>-2.221</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-14.883</v>
@@ -2006,25 +2006,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.906392</v>
+        <v>-1.896372</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5.651765</v>
+        <v>-5.417799</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9.782</v>
+        <v>-9.41</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10.192</v>
+        <v>-9.372</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.777</v>
+        <v>-4.441</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.923</v>
+        <v>-3.677</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.273</v>
+        <v>-2.169</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-14.846</v>
@@ -2148,25 +2148,25 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -38782,10 +38782,10 @@
         </is>
       </c>
       <c r="K330" s="5" t="n">
-        <v>2.221</v>
+        <v>-2.221</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>14.883</v>
+        <v>-14.883</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
@@ -44308,10 +44308,10 @@
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>2.596</v>
+        <v>-2.596</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>15.817</v>
+        <v>-15.817</v>
       </c>
       <c r="M389" t="inlineStr">
         <is>
@@ -44950,25 +44950,25 @@
         </is>
       </c>
       <c r="E396" s="5" t="n">
-        <v>1.901382</v>
+        <v>-1.901382</v>
       </c>
       <c r="F396" s="5" t="n">
-        <v>5.534782</v>
+        <v>-5.534782</v>
       </c>
       <c r="G396" s="5" t="n">
-        <v>9.596</v>
+        <v>-9.596</v>
       </c>
       <c r="H396" s="5" t="n">
-        <v>9.782</v>
+        <v>-9.782</v>
       </c>
       <c r="I396" s="5" t="n">
-        <v>4.609</v>
+        <v>-4.609</v>
       </c>
       <c r="J396" s="5" t="n">
-        <v>3.8</v>
+        <v>-3.8</v>
       </c>
       <c r="K396" s="5" t="n">
-        <v>2.221</v>
+        <v>-2.221</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
@@ -47085,13 +47085,13 @@
         </is>
       </c>
       <c r="F419" s="5" t="n">
-        <v>5.534782</v>
+        <v>-5.534782</v>
       </c>
       <c r="G419" s="5" t="n">
-        <v>9.596</v>
+        <v>-9.596</v>
       </c>
       <c r="H419" s="5" t="n">
-        <v>9.782</v>
+        <v>-9.782</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LPK.xlsx
+++ b/output/pdf_financials_xlsx/LPK.xlsx
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001694</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>0.315</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-34.033407</v>
+        <v>-34.035101</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>20.672959</v>
@@ -2033,7 +2033,7 @@
         <v>0.315</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-34.032699</v>
+        <v>-34.034393</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>20.673667</v>
@@ -2318,31 +2318,31 @@
         <v>0.112</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.656</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.076122</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.006024</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.121215</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.070595</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.034965</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.029397</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.131448</v>
       </c>
     </row>
     <row r="35">
@@ -2428,31 +2428,31 @@
         <v>0.112</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.797</v>
+        <v>5.453</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.076122</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.006024</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.121215</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.070595</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.034965</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.029397</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.131448</v>
       </c>
     </row>
     <row r="37">
@@ -3088,31 +3088,31 @@
         <v>0.056</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.917</v>
+        <v>0.261</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.268</v>
+        <v>0.035</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.088356</v>
+        <v>0.012234</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.007625</v>
+        <v>0.001601</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.123202</v>
+        <v>0.001987</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.071448</v>
+        <v>0.000853</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.034965</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.029397</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.131448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -41010,7 +41010,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -44660,7 +44660,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">

--- a/output/pdf_financials_xlsx/LPK.xlsx
+++ b/output/pdf_financials_xlsx/LPK.xlsx
@@ -6373,31 +6373,31 @@
         <v>0.168</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.296</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.153317</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.067443</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.084797</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.077931</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.026064</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.022225</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.045686</v>
       </c>
     </row>
     <row r="108">
@@ -6535,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -6572,31 +6572,31 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.079527</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.225888</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.309</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.107</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.078</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.062</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.202</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -6813,10 +6813,10 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.581</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>3.391</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -7869,31 +7869,31 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.079527</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.225888</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.309</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.107</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.078</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.062</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.202</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -7924,31 +7924,31 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.55674</v>
+        <v>-0.636267</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-3.337779</v>
+        <v>-3.563667</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-8.081</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-6.65</v>
+        <v>-6.757</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-4.376</v>
+        <v>-4.454</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-2.786</v>
+        <v>-2.848</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.725</v>
+        <v>-1.728</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-2.783</v>
+        <v>-2.787</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-1.443</v>
+        <v>-1.645</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-0.364431</v>
@@ -20878,7 +20878,11 @@
           <t>Share-based compensation expense (Note 9)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -22222,7 +22226,11 @@
           <t>Share-based compensation expense (Note 9)</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -22812,7 +22820,11 @@
           <t>Share-based compensation expense (Note 8)</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -23840,7 +23852,11 @@
           <t>Share-based compensation expense (Note 10)</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -25936,7 +25952,11 @@
           <t>Share-based compensation expense (Note 12)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -26310,7 +26330,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -26404,7 +26428,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -27150,7 +27178,11 @@
           <t>Share-based compensation expense (Note 13)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -29244,7 +29276,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -30854,7 +30890,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -36962,7 +37002,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E310" s="5" t="n">
         <v>-0.079527</v>
       </c>
